--- a/dl/greek-cities-west-asia.xlsx
+++ b/dl/greek-cities-west-asia.xlsx
@@ -11322,7 +11322,7 @@
     <t xml:space="preserve">Achaia/Achais</t>
   </si>
   <si>
-    <t xml:space="preserve">Seleucid foundation (Appian, Syr. 57; Strabo 11.10.1 places Achaia in Areia; Pliny 6.48 has Heraclea refounded as Achais), in present-day Afghanistan or Turkmenistan: counted in the companion set Greek Cities of Central and South Asia (in preparation).</t>
+    <t xml:space="preserve">Seleucid foundation (Appian, Syr. 57; Strabo 11.10.1 places Achaia in Areia; Pliny 6.48 has Heraclea refounded as Achais), in present-day Afghanistan or Turkmenistan: counted in the companion set Greek Cities of Central and South Asia.</t>
   </si>
   <si>
     <t xml:space="preserve">Shushtar (Tostar)</t>
@@ -11355,7 +11355,7 @@
     <t xml:space="preserve">Afghanistan</t>
   </si>
   <si>
-    <t xml:space="preserve">In present-day Afghanistan: counted in the companion set Greek Cities of Central and South Asia (in preparation).</t>
+    <t xml:space="preserve">In present-day Afghanistan: counted in the companion set Greek Cities of Central and South Asia.</t>
   </si>
   <si>
     <t xml:space="preserve">Prophthasia (Farah)</t>
@@ -11370,13 +11370,13 @@
     <t xml:space="preserve">Turkmenistan</t>
   </si>
   <si>
-    <t xml:space="preserve">In present-day Turkmenistan: counted in the companion set Greek Cities of Central and South Asia (in preparation).</t>
+    <t xml:space="preserve">In present-day Turkmenistan: counted in the companion set Greek Cities of Central and South Asia.</t>
   </si>
   <si>
     <t xml:space="preserve">Nisa (Mithradatkert)</t>
   </si>
   <si>
-    <t xml:space="preserve">In present-day Turkmenistan; the companion set Greek Cities of Central and South Asia (in preparation) leaves it out too: an Arsacid royal fortress, whose Greek art belongs to the court and whose documents are Parthian.</t>
+    <t xml:space="preserve">In present-day Turkmenistan; the companion set Greek Cities of Central and South Asia leaves it out too: an Arsacid royal fortress, whose Greek art belongs to the court and whose documents are Parthian.</t>
   </si>
   <si>
     <t xml:space="preserve">Eruandashat (Yervandashat)</t>
@@ -11631,7 +11631,7 @@
     <t xml:space="preserve">Alexandria and Alexandropolis in Sakastane</t>
   </si>
   <si>
-    <t xml:space="preserve">Named by Isidore of Charax (Parthian Stations 18) among the towns of Sakastane, which lies mostly in Afghanistan; nothing places them in Iranian Sistan. Alexandropolis is counted in the companion set Greek Cities of Central and South Asia (in preparation) (the Alexandria there is taken as a scribal repetition).</t>
+    <t xml:space="preserve">Named by Isidore of Charax (Parthian Stations 18) among the towns of Sakastane, which lies mostly in Afghanistan; nothing places them in Iranian Sistan. Alexandropolis is counted in the companion set Greek Cities of Central and South Asia (the Alexandria there is taken as a scribal repetition).</t>
   </si>
   <si>
     <t xml:space="preserve">Corada (Phoenice Libanensis)</t>
@@ -11814,7 +11814,7 @@
     <t xml:space="preserve">Soteira (Parthia)</t>
   </si>
   <si>
-    <t xml:space="preserve">Seleucus I's foundation in Parthia (Appian, Syr. 57); Ptolemy lists a Sotira in Areia, so it is counted in the companion set Greek Cities of Central and South Asia (in preparation).</t>
+    <t xml:space="preserve">Seleucus I's foundation in Parthia (Appian, Syr. 57); Ptolemy lists a Sotira in Areia, so it is counted in the companion set Greek Cities of Central and South Asia.</t>
   </si>
   <si>
     <t xml:space="preserve">Dahan-i Ghulaman (Zranka?)</t>
